--- a/output/yearly_population_iteration_85_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_85_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5335</v>
+        <v>6617</v>
       </c>
       <c r="C2" t="n">
-        <v>5262</v>
+        <v>14366</v>
       </c>
       <c r="D2" t="n">
-        <v>21715</v>
+        <v>29520</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3499</v>
+        <v>3503</v>
       </c>
       <c r="C3" t="n">
-        <v>7314</v>
+        <v>6872</v>
       </c>
       <c r="D3" t="n">
-        <v>9947</v>
+        <v>16371</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2617</v>
+        <v>2796</v>
       </c>
       <c r="C4" t="n">
-        <v>6537</v>
+        <v>6420</v>
       </c>
       <c r="D4" t="n">
-        <v>4436</v>
+        <v>6593</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1724</v>
+        <v>1663</v>
       </c>
       <c r="C5" t="n">
-        <v>5132</v>
+        <v>5024</v>
       </c>
       <c r="D5" t="n">
-        <v>1915</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>996</v>
+        <v>928</v>
       </c>
       <c r="C6" t="n">
-        <v>3954</v>
+        <v>3139</v>
       </c>
       <c r="D6" t="n">
-        <v>986</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="C7" t="n">
-        <v>2625</v>
+        <v>2070</v>
       </c>
       <c r="D7" t="n">
-        <v>623</v>
+        <v>631</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C8" t="n">
-        <v>1279</v>
+        <v>1016</v>
       </c>
       <c r="D8" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C9" t="n">
-        <v>476</v>
+        <v>420</v>
       </c>
       <c r="D9" t="n">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
         <v>164</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6878</v>
+        <v>5862</v>
       </c>
       <c r="C2" t="n">
-        <v>19299</v>
+        <v>11411</v>
       </c>
       <c r="D2" t="n">
-        <v>18895</v>
+        <v>26886</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3538</v>
+        <v>3931</v>
       </c>
       <c r="C3" t="n">
-        <v>5643</v>
+        <v>8996</v>
       </c>
       <c r="D3" t="n">
-        <v>10879</v>
+        <v>17059</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2552</v>
+        <v>2676</v>
       </c>
       <c r="C4" t="n">
-        <v>6766</v>
+        <v>6499</v>
       </c>
       <c r="D4" t="n">
-        <v>5200</v>
+        <v>7988</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1857</v>
+        <v>1881</v>
       </c>
       <c r="C5" t="n">
-        <v>5609</v>
+        <v>5501</v>
       </c>
       <c r="D5" t="n">
-        <v>2225</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1185</v>
+        <v>1124</v>
       </c>
       <c r="C6" t="n">
-        <v>4436</v>
+        <v>3941</v>
       </c>
       <c r="D6" t="n">
-        <v>1115</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>622</v>
+        <v>592</v>
       </c>
       <c r="C7" t="n">
-        <v>3171</v>
+        <v>2509</v>
       </c>
       <c r="D7" t="n">
-        <v>663</v>
+        <v>672</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C8" t="n">
-        <v>1845</v>
+        <v>1449</v>
       </c>
       <c r="D8" t="n">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C9" t="n">
-        <v>793</v>
+        <v>665</v>
       </c>
       <c r="D9" t="n">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C10" t="n">
-        <v>325</v>
+        <v>297</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11">
@@ -1217,7 +1217,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
         <v>186</v>
@@ -1237,7 +1237,7 @@
         <v>139</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -1265,7 +1265,7 @@
         <v>82</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1318,7 +1318,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7097</v>
+        <v>6901</v>
       </c>
       <c r="C2" t="n">
-        <v>14168</v>
+        <v>13438</v>
       </c>
       <c r="D2" t="n">
-        <v>24580</v>
+        <v>33748</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3934</v>
+        <v>3845</v>
       </c>
       <c r="C3" t="n">
-        <v>9826</v>
+        <v>8852</v>
       </c>
       <c r="D3" t="n">
-        <v>11144</v>
+        <v>17146</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2528</v>
+        <v>2698</v>
       </c>
       <c r="C4" t="n">
-        <v>6085</v>
+        <v>7356</v>
       </c>
       <c r="D4" t="n">
-        <v>5809</v>
+        <v>8974</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1893</v>
+        <v>1967</v>
       </c>
       <c r="C5" t="n">
-        <v>5969</v>
+        <v>5745</v>
       </c>
       <c r="D5" t="n">
-        <v>2585</v>
+        <v>3480</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1317</v>
+        <v>1286</v>
       </c>
       <c r="C6" t="n">
-        <v>4816</v>
+        <v>4535</v>
       </c>
       <c r="D6" t="n">
-        <v>1238</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>752</v>
+        <v>714</v>
       </c>
       <c r="C7" t="n">
-        <v>3634</v>
+        <v>3044</v>
       </c>
       <c r="D7" t="n">
-        <v>718</v>
+        <v>734</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="C8" t="n">
-        <v>2351</v>
+        <v>1839</v>
       </c>
       <c r="D8" t="n">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C9" t="n">
-        <v>1166</v>
+        <v>956</v>
       </c>
       <c r="D9" t="n">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>486</v>
+        <v>423</v>
       </c>
       <c r="D10" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11">
@@ -1528,10 +1528,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="D11" t="n">
         <v>208</v>
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1618,7 +1618,7 @@
         <v>41</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1629,7 +1629,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6590</v>
+        <v>6413</v>
       </c>
       <c r="C2" t="n">
-        <v>9860</v>
+        <v>9352</v>
       </c>
       <c r="D2" t="n">
-        <v>20198</v>
+        <v>27821</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4600</v>
+        <v>4690</v>
       </c>
       <c r="C3" t="n">
-        <v>13476</v>
+        <v>13002</v>
       </c>
       <c r="D3" t="n">
-        <v>11947</v>
+        <v>18393</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1749</v>
+        <v>1817</v>
       </c>
       <c r="C4" t="n">
-        <v>9001</v>
+        <v>9469</v>
       </c>
       <c r="D4" t="n">
-        <v>5578</v>
+        <v>8263</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1216</v>
+        <v>1188</v>
       </c>
       <c r="C5" t="n">
-        <v>4719</v>
+        <v>4444</v>
       </c>
       <c r="D5" t="n">
-        <v>1908</v>
+        <v>2279</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>694</v>
+        <v>659</v>
       </c>
       <c r="C6" t="n">
-        <v>3561</v>
+        <v>2983</v>
       </c>
       <c r="D6" t="n">
-        <v>703</v>
+        <v>719</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="C7" t="n">
-        <v>2303</v>
+        <v>1802</v>
       </c>
       <c r="D7" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C8" t="n">
-        <v>1142</v>
+        <v>936</v>
       </c>
       <c r="D8" t="n">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>476</v>
+        <v>414</v>
       </c>
       <c r="D9" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10">
@@ -1825,10 +1825,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="D10" t="n">
         <v>203</v>
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16">
@@ -1915,7 +1915,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
         <v>37</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4069</v>
+        <v>3951</v>
       </c>
       <c r="C2" t="n">
-        <v>4946</v>
+        <v>4544</v>
       </c>
       <c r="D2" t="n">
-        <v>13936</v>
+        <v>20205</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4681</v>
+        <v>4678</v>
       </c>
       <c r="C3" t="n">
-        <v>10800</v>
+        <v>10356</v>
       </c>
       <c r="D3" t="n">
-        <v>12495</v>
+        <v>18792</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2425</v>
+        <v>2495</v>
       </c>
       <c r="C4" t="n">
-        <v>11092</v>
+        <v>11138</v>
       </c>
       <c r="D4" t="n">
-        <v>6379</v>
+        <v>9549</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1346</v>
+        <v>1337</v>
       </c>
       <c r="C5" t="n">
-        <v>6573</v>
+        <v>6590</v>
       </c>
       <c r="D5" t="n">
-        <v>2362</v>
+        <v>3022</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>811</v>
+        <v>775</v>
       </c>
       <c r="C6" t="n">
-        <v>4168</v>
+        <v>3656</v>
       </c>
       <c r="D6" t="n">
-        <v>819</v>
+        <v>866</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C7" t="n">
-        <v>2803</v>
+        <v>2243</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>500</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C8" t="n">
-        <v>1495</v>
+        <v>1218</v>
       </c>
       <c r="D8" t="n">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C9" t="n">
-        <v>516</v>
+        <v>449</v>
       </c>
       <c r="D9" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10">
@@ -2139,7 +2139,7 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="D10" t="n">
         <v>209</v>
@@ -2167,7 +2167,7 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D12" t="n">
         <v>131</v>
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -2212,7 +2212,7 @@
         <v>39</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
         <v>36</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4106</v>
+        <v>3634</v>
       </c>
       <c r="C2" t="n">
-        <v>11374</v>
+        <v>6878</v>
       </c>
       <c r="D2" t="n">
-        <v>14510</v>
+        <v>18826</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3727</v>
+        <v>3687</v>
       </c>
       <c r="C3" t="n">
-        <v>7162</v>
+        <v>6788</v>
       </c>
       <c r="D3" t="n">
-        <v>11851</v>
+        <v>17721</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2876</v>
+        <v>2933</v>
       </c>
       <c r="C4" t="n">
-        <v>10721</v>
+        <v>10637</v>
       </c>
       <c r="D4" t="n">
-        <v>7183</v>
+        <v>10767</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1593</v>
+        <v>1589</v>
       </c>
       <c r="C5" t="n">
-        <v>8581</v>
+        <v>8504</v>
       </c>
       <c r="D5" t="n">
-        <v>2907</v>
+        <v>3932</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>952</v>
+        <v>926</v>
       </c>
       <c r="C6" t="n">
-        <v>5167</v>
+        <v>4889</v>
       </c>
       <c r="D6" t="n">
-        <v>1030</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>432</v>
+        <v>420</v>
       </c>
       <c r="C7" t="n">
-        <v>3404</v>
+        <v>2859</v>
       </c>
       <c r="D7" t="n">
-        <v>535</v>
+        <v>545</v>
       </c>
     </row>
     <row r="8">
@@ -2422,7 +2422,7 @@
         <v>152</v>
       </c>
       <c r="C8" t="n">
-        <v>2021</v>
+        <v>1631</v>
       </c>
       <c r="D8" t="n">
         <v>349</v>
@@ -2436,10 +2436,10 @@
         <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>875</v>
+        <v>732</v>
       </c>
       <c r="D9" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>335</v>
+        <v>309</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13">
@@ -2495,7 +2495,7 @@
         <v>72</v>
       </c>
       <c r="D13" t="n">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D17" t="n">
         <v>23</v>
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2491</v>
+        <v>2217</v>
       </c>
       <c r="C2" t="n">
-        <v>5535</v>
+        <v>3333</v>
       </c>
       <c r="D2" t="n">
-        <v>10113</v>
+        <v>13144</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3681</v>
+        <v>3549</v>
       </c>
       <c r="C3" t="n">
-        <v>8315</v>
+        <v>6632</v>
       </c>
       <c r="D3" t="n">
-        <v>11862</v>
+        <v>17438</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3155</v>
+        <v>3198</v>
       </c>
       <c r="C4" t="n">
-        <v>10433</v>
+        <v>10254</v>
       </c>
       <c r="D4" t="n">
-        <v>7740</v>
+        <v>11595</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1649</v>
+        <v>1641</v>
       </c>
       <c r="C5" t="n">
-        <v>10321</v>
+        <v>10214</v>
       </c>
       <c r="D5" t="n">
-        <v>3080</v>
+        <v>4172</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>777</v>
+        <v>747</v>
       </c>
       <c r="C6" t="n">
-        <v>6172</v>
+        <v>5735</v>
       </c>
       <c r="D6" t="n">
-        <v>1029</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="7">
@@ -2719,10 +2719,10 @@
         <v>140</v>
       </c>
       <c r="C7" t="n">
-        <v>3588</v>
+        <v>2968</v>
       </c>
       <c r="D7" t="n">
-        <v>543</v>
+        <v>551</v>
       </c>
     </row>
     <row r="8">
@@ -2733,10 +2733,10 @@
         <v>48</v>
       </c>
       <c r="C8" t="n">
-        <v>1451</v>
+        <v>1196</v>
       </c>
       <c r="D8" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>328</v>
+        <v>302</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D10" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12">
@@ -2792,7 +2792,7 @@
         <v>70</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D16" t="n">
         <v>22</v>
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3633</v>
+        <v>2549</v>
       </c>
       <c r="C2" t="n">
-        <v>4640</v>
+        <v>2791</v>
       </c>
       <c r="D2" t="n">
-        <v>13858</v>
+        <v>11042</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2741</v>
+        <v>2566</v>
       </c>
       <c r="C3" t="n">
-        <v>6320</v>
+        <v>4654</v>
       </c>
       <c r="D3" t="n">
-        <v>10859</v>
+        <v>15744</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2965</v>
+        <v>2947</v>
       </c>
       <c r="C4" t="n">
-        <v>9340</v>
+        <v>8406</v>
       </c>
       <c r="D4" t="n">
-        <v>8137</v>
+        <v>12139</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1980</v>
+        <v>1987</v>
       </c>
       <c r="C5" t="n">
-        <v>10253</v>
+        <v>10116</v>
       </c>
       <c r="D5" t="n">
-        <v>3657</v>
+        <v>5114</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>988</v>
+        <v>972</v>
       </c>
       <c r="C6" t="n">
-        <v>7851</v>
+        <v>7546</v>
       </c>
       <c r="D6" t="n">
-        <v>1301</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>290</v>
+        <v>276</v>
       </c>
       <c r="C7" t="n">
-        <v>4644</v>
+        <v>4082</v>
       </c>
       <c r="D7" t="n">
-        <v>594</v>
+        <v>615</v>
       </c>
     </row>
     <row r="8">
@@ -3044,10 +3044,10 @@
         <v>64</v>
       </c>
       <c r="C8" t="n">
-        <v>2211</v>
+        <v>1826</v>
       </c>
       <c r="D8" t="n">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>675</v>
+        <v>582</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="D10" t="n">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3103,7 +3103,7 @@
         <v>80</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3131,7 +3131,7 @@
         <v>45</v>
       </c>
       <c r="D14" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2391</v>
+        <v>1785</v>
       </c>
       <c r="C2" t="n">
-        <v>4276</v>
+        <v>2796</v>
       </c>
       <c r="D2" t="n">
-        <v>9810</v>
+        <v>8280</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2640</v>
+        <v>2247</v>
       </c>
       <c r="C3" t="n">
-        <v>5236</v>
+        <v>3640</v>
       </c>
       <c r="D3" t="n">
-        <v>10621</v>
+        <v>14386</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2649</v>
+        <v>2595</v>
       </c>
       <c r="C4" t="n">
-        <v>8165</v>
+        <v>6951</v>
       </c>
       <c r="D4" t="n">
-        <v>8307</v>
+        <v>12336</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2158</v>
+        <v>2161</v>
       </c>
       <c r="C5" t="n">
-        <v>10117</v>
+        <v>9703</v>
       </c>
       <c r="D5" t="n">
-        <v>4089</v>
+        <v>5798</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1140</v>
+        <v>1125</v>
       </c>
       <c r="C6" t="n">
-        <v>8877</v>
+        <v>8607</v>
       </c>
       <c r="D6" t="n">
-        <v>1492</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="C7" t="n">
-        <v>5683</v>
+        <v>5141</v>
       </c>
       <c r="D7" t="n">
-        <v>651</v>
+        <v>684</v>
       </c>
     </row>
     <row r="8">
@@ -3355,10 +3355,10 @@
         <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>2778</v>
+        <v>2330</v>
       </c>
       <c r="D8" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>738</v>
+        <v>641</v>
       </c>
       <c r="D9" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="D10" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11">
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D12" t="n">
         <v>91</v>
@@ -3428,7 +3428,7 @@
         <v>44</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4397</v>
+        <v>2700</v>
       </c>
       <c r="C2" t="n">
-        <v>6652</v>
+        <v>3407</v>
       </c>
       <c r="D2" t="n">
-        <v>9500</v>
+        <v>14143</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2154</v>
+        <v>1763</v>
       </c>
       <c r="C3" t="n">
-        <v>4352</v>
+        <v>2966</v>
       </c>
       <c r="D3" t="n">
-        <v>9867</v>
+        <v>12804</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2299</v>
+        <v>2154</v>
       </c>
       <c r="C4" t="n">
-        <v>6814</v>
+        <v>5471</v>
       </c>
       <c r="D4" t="n">
-        <v>8365</v>
+        <v>12236</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2137</v>
+        <v>2125</v>
       </c>
       <c r="C5" t="n">
-        <v>9156</v>
+        <v>8444</v>
       </c>
       <c r="D5" t="n">
-        <v>4451</v>
+        <v>6382</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1347</v>
+        <v>1337</v>
       </c>
       <c r="C6" t="n">
-        <v>9258</v>
+        <v>8937</v>
       </c>
       <c r="D6" t="n">
-        <v>1797</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>464</v>
+        <v>453</v>
       </c>
       <c r="C7" t="n">
-        <v>6807</v>
+        <v>6361</v>
       </c>
       <c r="D7" t="n">
-        <v>743</v>
+        <v>812</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>3772</v>
+        <v>3288</v>
       </c>
       <c r="D8" t="n">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="9">
@@ -3680,10 +3680,10 @@
         <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>1357</v>
+        <v>1153</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>378</v>
+        <v>342</v>
       </c>
       <c r="D10" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11">
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D11" t="n">
         <v>137</v>
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D12" t="n">
         <v>93</v>
@@ -3739,7 +3739,7 @@
         <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5820</v>
+        <v>6169</v>
       </c>
       <c r="C2" t="n">
-        <v>12354</v>
+        <v>8979</v>
       </c>
       <c r="D2" t="n">
-        <v>5586</v>
+        <v>5621</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3210</v>
+        <v>1973</v>
       </c>
       <c r="C2" t="n">
-        <v>3937</v>
+        <v>2016</v>
       </c>
       <c r="D2" t="n">
-        <v>7068</v>
+        <v>10523</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2915</v>
+        <v>2412</v>
       </c>
       <c r="C3" t="n">
-        <v>5292</v>
+        <v>3380</v>
       </c>
       <c r="D3" t="n">
-        <v>10646</v>
+        <v>14023</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3149</v>
+        <v>3063</v>
       </c>
       <c r="C4" t="n">
-        <v>9886</v>
+        <v>8183</v>
       </c>
       <c r="D4" t="n">
-        <v>8456</v>
+        <v>12338</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1264</v>
+        <v>1255</v>
       </c>
       <c r="C5" t="n">
-        <v>13153</v>
+        <v>12531</v>
       </c>
       <c r="D5" t="n">
-        <v>4102</v>
+        <v>5747</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>428</v>
+        <v>418</v>
       </c>
       <c r="C6" t="n">
-        <v>8303</v>
+        <v>7810</v>
       </c>
       <c r="D6" t="n">
-        <v>1503</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C7" t="n">
-        <v>3696</v>
+        <v>3222</v>
       </c>
       <c r="D7" t="n">
-        <v>506</v>
+        <v>518</v>
       </c>
     </row>
     <row r="8">
@@ -4288,10 +4288,10 @@
         <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>1329</v>
+        <v>1129</v>
       </c>
       <c r="D8" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>370</v>
+        <v>335</v>
       </c>
       <c r="D9" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10">
@@ -4316,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
         <v>134</v>
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D11" t="n">
         <v>91</v>
@@ -4347,7 +4347,7 @@
         <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6639</v>
+        <v>6208</v>
       </c>
       <c r="C2" t="n">
-        <v>7640</v>
+        <v>6894</v>
       </c>
       <c r="D2" t="n">
-        <v>12760</v>
+        <v>8810</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2473</v>
+        <v>2621</v>
       </c>
       <c r="C3" t="n">
-        <v>6226</v>
+        <v>4525</v>
       </c>
       <c r="D3" t="n">
-        <v>1577</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" t="n">
         <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5004</v>
+        <v>4074</v>
       </c>
       <c r="C2" t="n">
-        <v>10812</v>
+        <v>7474</v>
       </c>
       <c r="D2" t="n">
-        <v>11557</v>
+        <v>13221</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3741</v>
+        <v>3627</v>
       </c>
       <c r="C3" t="n">
-        <v>6059</v>
+        <v>5058</v>
       </c>
       <c r="D3" t="n">
-        <v>3339</v>
+        <v>2680</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1108</v>
+        <v>1172</v>
       </c>
       <c r="C4" t="n">
-        <v>3691</v>
+        <v>2693</v>
       </c>
       <c r="D4" t="n">
-        <v>1499</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C9" t="n">
         <v>232</v>
@@ -4935,10 +4935,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
         <v>352</v>
@@ -4952,7 +4952,7 @@
         <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5022,7 +5022,7 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
         <v>98</v>
@@ -5036,7 +5036,7 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
         <v>78</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4872</v>
+        <v>4313</v>
       </c>
       <c r="C2" t="n">
-        <v>5348</v>
+        <v>4829</v>
       </c>
       <c r="D2" t="n">
-        <v>10782</v>
+        <v>21490</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3587</v>
+        <v>3173</v>
       </c>
       <c r="C3" t="n">
-        <v>7546</v>
+        <v>5518</v>
       </c>
       <c r="D3" t="n">
-        <v>4413</v>
+        <v>4173</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2062</v>
+        <v>2033</v>
       </c>
       <c r="C4" t="n">
-        <v>4897</v>
+        <v>3976</v>
       </c>
       <c r="D4" t="n">
-        <v>1806</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>506</v>
+        <v>541</v>
       </c>
       <c r="C5" t="n">
-        <v>2114</v>
+        <v>1568</v>
       </c>
       <c r="D5" t="n">
-        <v>1204</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8">
@@ -5224,7 +5224,7 @@
         <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9">
@@ -5238,7 +5238,7 @@
         <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5277,10 +5277,10 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13">
@@ -5294,7 +5294,7 @@
         <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14">
@@ -5305,7 +5305,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
         <v>148</v>
@@ -5316,10 +5316,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5066</v>
+        <v>4689</v>
       </c>
       <c r="C2" t="n">
-        <v>7895</v>
+        <v>7014</v>
       </c>
       <c r="D2" t="n">
-        <v>15464</v>
+        <v>29800</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3443</v>
+        <v>3054</v>
       </c>
       <c r="C3" t="n">
-        <v>5583</v>
+        <v>4494</v>
       </c>
       <c r="D3" t="n">
-        <v>5070</v>
+        <v>6511</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2372</v>
+        <v>2223</v>
       </c>
       <c r="C4" t="n">
-        <v>6219</v>
+        <v>4722</v>
       </c>
       <c r="D4" t="n">
-        <v>2226</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="C5" t="n">
-        <v>3512</v>
+        <v>2768</v>
       </c>
       <c r="D5" t="n">
-        <v>1259</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="6">
@@ -5501,10 +5501,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="C6" t="n">
-        <v>1201</v>
+        <v>942</v>
       </c>
       <c r="D6" t="n">
         <v>946</v>
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C7" t="n">
         <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C8" t="n">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D8" t="n">
-        <v>478</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
         <v>286</v>
@@ -5588,10 +5588,10 @@
         <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13">
@@ -5605,7 +5605,7 @@
         <v>128</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="14">
@@ -5616,7 +5616,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D14" t="n">
         <v>148</v>
@@ -5630,7 +5630,7 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
         <v>122</v>
@@ -5658,7 +5658,7 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
         <v>79</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6527</v>
+        <v>7048</v>
       </c>
       <c r="C2" t="n">
-        <v>9382</v>
+        <v>13131</v>
       </c>
       <c r="D2" t="n">
-        <v>19243</v>
+        <v>29872</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3101</v>
+        <v>2797</v>
       </c>
       <c r="C3" t="n">
-        <v>5526</v>
+        <v>4736</v>
       </c>
       <c r="D3" t="n">
-        <v>5920</v>
+        <v>9023</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1782</v>
+        <v>1628</v>
       </c>
       <c r="C4" t="n">
-        <v>4758</v>
+        <v>3764</v>
       </c>
       <c r="D4" t="n">
-        <v>2333</v>
+        <v>2467</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>886</v>
+        <v>864</v>
       </c>
       <c r="C5" t="n">
-        <v>3590</v>
+        <v>2742</v>
       </c>
       <c r="D5" t="n">
-        <v>1114</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="C6" t="n">
-        <v>1570</v>
+        <v>1254</v>
       </c>
       <c r="D6" t="n">
-        <v>760</v>
+        <v>756</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C7" t="n">
-        <v>490</v>
+        <v>407</v>
       </c>
       <c r="D7" t="n">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C8" t="n">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="D9" t="n">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="12">
@@ -5902,7 +5902,7 @@
         <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14">
@@ -5969,7 +5969,7 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
         <v>50</v>
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4871</v>
+        <v>5685</v>
       </c>
       <c r="C2" t="n">
-        <v>10384</v>
+        <v>7143</v>
       </c>
       <c r="D2" t="n">
-        <v>15651</v>
+        <v>35018</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3983</v>
+        <v>4108</v>
       </c>
       <c r="C3" t="n">
-        <v>6691</v>
+        <v>8300</v>
       </c>
       <c r="D3" t="n">
-        <v>7722</v>
+        <v>11861</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2117</v>
+        <v>1942</v>
       </c>
       <c r="C4" t="n">
-        <v>5123</v>
+        <v>4273</v>
       </c>
       <c r="D4" t="n">
-        <v>2962</v>
+        <v>3690</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1191</v>
+        <v>1114</v>
       </c>
       <c r="C5" t="n">
-        <v>4199</v>
+        <v>3257</v>
       </c>
       <c r="D5" t="n">
-        <v>1325</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>554</v>
+        <v>544</v>
       </c>
       <c r="C6" t="n">
-        <v>2694</v>
+        <v>2095</v>
       </c>
       <c r="D6" t="n">
-        <v>817</v>
+        <v>806</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="C7" t="n">
-        <v>1093</v>
+        <v>888</v>
       </c>
       <c r="D7" t="n">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>367</v>
+        <v>323</v>
       </c>
       <c r="D8" t="n">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D9" t="n">
-        <v>285</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
         <v>199</v>
@@ -6213,7 +6213,7 @@
         <v>101</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13">
@@ -6227,7 +6227,7 @@
         <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14">
@@ -6235,7 +6235,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
         <v>63</v>
@@ -6252,10 +6252,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6305,7 +6305,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
@@ -6322,7 +6322,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6339,7 +6339,7 @@
         <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5016</v>
+        <v>4508</v>
       </c>
       <c r="C2" t="n">
-        <v>9254</v>
+        <v>9124</v>
       </c>
       <c r="D2" t="n">
-        <v>22972</v>
+        <v>33266</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3635</v>
+        <v>4013</v>
       </c>
       <c r="C3" t="n">
-        <v>7515</v>
+        <v>6638</v>
       </c>
       <c r="D3" t="n">
-        <v>8434</v>
+        <v>14712</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2584</v>
+        <v>2591</v>
       </c>
       <c r="C4" t="n">
-        <v>5889</v>
+        <v>6465</v>
       </c>
       <c r="D4" t="n">
-        <v>3785</v>
+        <v>5146</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1452</v>
+        <v>1333</v>
       </c>
       <c r="C5" t="n">
-        <v>4568</v>
+        <v>3745</v>
       </c>
       <c r="D5" t="n">
-        <v>1583</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>781</v>
+        <v>754</v>
       </c>
       <c r="C6" t="n">
-        <v>3457</v>
+        <v>2684</v>
       </c>
       <c r="D6" t="n">
-        <v>885</v>
+        <v>889</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C7" t="n">
-        <v>1924</v>
+        <v>1505</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>587</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="C8" t="n">
-        <v>729</v>
+        <v>610</v>
       </c>
       <c r="D8" t="n">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>282</v>
+        <v>265</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D10" t="n">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
         <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
@@ -6552,7 +6552,7 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -6566,7 +6566,7 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_85_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_85_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6617</v>
+        <v>4612</v>
       </c>
       <c r="C2" t="n">
-        <v>14366</v>
+        <v>12880</v>
       </c>
       <c r="D2" t="n">
-        <v>29520</v>
+        <v>25593</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3503</v>
+        <v>3167</v>
       </c>
       <c r="C3" t="n">
-        <v>6872</v>
+        <v>4566</v>
       </c>
       <c r="D3" t="n">
-        <v>16371</v>
+        <v>16718</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2796</v>
+        <v>2430</v>
       </c>
       <c r="C4" t="n">
-        <v>6420</v>
+        <v>5683</v>
       </c>
       <c r="D4" t="n">
-        <v>6593</v>
+        <v>8907</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1663</v>
+        <v>1623</v>
       </c>
       <c r="C5" t="n">
-        <v>5024</v>
+        <v>4871</v>
       </c>
       <c r="D5" t="n">
-        <v>2244</v>
+        <v>3323</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>928</v>
+        <v>952</v>
       </c>
       <c r="C6" t="n">
-        <v>3139</v>
+        <v>3298</v>
       </c>
       <c r="D6" t="n">
-        <v>1000</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>466</v>
+        <v>455</v>
       </c>
       <c r="C7" t="n">
-        <v>2070</v>
+        <v>1954</v>
       </c>
       <c r="D7" t="n">
-        <v>631</v>
+        <v>671</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="C8" t="n">
-        <v>1016</v>
+        <v>937</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>420</v>
+        <v>395</v>
       </c>
       <c r="D9" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1010,7 +1010,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5862</v>
+        <v>5418</v>
       </c>
       <c r="C2" t="n">
-        <v>11411</v>
+        <v>12435</v>
       </c>
       <c r="D2" t="n">
-        <v>26886</v>
+        <v>24610</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3931</v>
+        <v>3131</v>
       </c>
       <c r="C3" t="n">
-        <v>8996</v>
+        <v>7284</v>
       </c>
       <c r="D3" t="n">
-        <v>17059</v>
+        <v>16962</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2676</v>
+        <v>2342</v>
       </c>
       <c r="C4" t="n">
-        <v>6499</v>
+        <v>5039</v>
       </c>
       <c r="D4" t="n">
-        <v>7988</v>
+        <v>9750</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1881</v>
+        <v>1737</v>
       </c>
       <c r="C5" t="n">
-        <v>5501</v>
+        <v>5089</v>
       </c>
       <c r="D5" t="n">
-        <v>2822</v>
+        <v>4079</v>
       </c>
     </row>
     <row r="6">
@@ -1150,10 +1150,10 @@
         <v>1124</v>
       </c>
       <c r="C6" t="n">
-        <v>3941</v>
+        <v>3960</v>
       </c>
       <c r="D6" t="n">
-        <v>1177</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="C7" t="n">
-        <v>2509</v>
+        <v>2513</v>
       </c>
       <c r="D7" t="n">
-        <v>672</v>
+        <v>755</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="C8" t="n">
-        <v>1449</v>
+        <v>1365</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>665</v>
+        <v>608</v>
       </c>
       <c r="D9" t="n">
-        <v>315</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="D10" t="n">
-        <v>251</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1293,7 +1293,7 @@
         <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1318,10 +1318,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1332,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6901</v>
+        <v>6780</v>
       </c>
       <c r="C2" t="n">
-        <v>13438</v>
+        <v>7810</v>
       </c>
       <c r="D2" t="n">
-        <v>33748</v>
+        <v>27491</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3845</v>
+        <v>3284</v>
       </c>
       <c r="C3" t="n">
-        <v>8852</v>
+        <v>8292</v>
       </c>
       <c r="D3" t="n">
-        <v>17146</v>
+        <v>16794</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2698</v>
+        <v>2264</v>
       </c>
       <c r="C4" t="n">
-        <v>7356</v>
+        <v>5834</v>
       </c>
       <c r="D4" t="n">
-        <v>8974</v>
+        <v>10398</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1967</v>
+        <v>1777</v>
       </c>
       <c r="C5" t="n">
-        <v>5745</v>
+        <v>4913</v>
       </c>
       <c r="D5" t="n">
-        <v>3480</v>
+        <v>4771</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1286</v>
+        <v>1241</v>
       </c>
       <c r="C6" t="n">
-        <v>4535</v>
+        <v>4380</v>
       </c>
       <c r="D6" t="n">
-        <v>1371</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="C7" t="n">
-        <v>3044</v>
+        <v>3054</v>
       </c>
       <c r="D7" t="n">
-        <v>734</v>
+        <v>857</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="C8" t="n">
-        <v>1839</v>
+        <v>1789</v>
       </c>
       <c r="D8" t="n">
-        <v>472</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C9" t="n">
-        <v>956</v>
+        <v>889</v>
       </c>
       <c r="D9" t="n">
-        <v>329</v>
+        <v>334</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>423</v>
+        <v>397</v>
       </c>
       <c r="D10" t="n">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1604,7 +1604,7 @@
         <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6413</v>
+        <v>6186</v>
       </c>
       <c r="C2" t="n">
-        <v>9352</v>
+        <v>5373</v>
       </c>
       <c r="D2" t="n">
-        <v>27821</v>
+        <v>22798</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4690</v>
+        <v>3971</v>
       </c>
       <c r="C3" t="n">
-        <v>13002</v>
+        <v>11299</v>
       </c>
       <c r="D3" t="n">
-        <v>18393</v>
+        <v>18510</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1817</v>
+        <v>1641</v>
       </c>
       <c r="C4" t="n">
-        <v>9469</v>
+        <v>7852</v>
       </c>
       <c r="D4" t="n">
-        <v>8263</v>
+        <v>10085</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1188</v>
+        <v>1146</v>
       </c>
       <c r="C5" t="n">
-        <v>4444</v>
+        <v>4292</v>
       </c>
       <c r="D5" t="n">
-        <v>2279</v>
+        <v>3105</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C6" t="n">
-        <v>2983</v>
+        <v>2992</v>
       </c>
       <c r="D6" t="n">
-        <v>719</v>
+        <v>839</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="C7" t="n">
-        <v>1802</v>
+        <v>1753</v>
       </c>
       <c r="D7" t="n">
-        <v>462</v>
+        <v>474</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C8" t="n">
-        <v>936</v>
+        <v>871</v>
       </c>
       <c r="D8" t="n">
-        <v>322</v>
+        <v>327</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>414</v>
+        <v>389</v>
       </c>
       <c r="D9" t="n">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10">
@@ -1828,10 +1828,10 @@
         <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="D10" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15">
@@ -1901,7 +1901,7 @@
         <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D18" t="n">
         <v>26</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3951</v>
+        <v>3911</v>
       </c>
       <c r="C2" t="n">
-        <v>4544</v>
+        <v>2538</v>
       </c>
       <c r="D2" t="n">
-        <v>20205</v>
+        <v>16588</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4678</v>
+        <v>4196</v>
       </c>
       <c r="C3" t="n">
-        <v>10356</v>
+        <v>7898</v>
       </c>
       <c r="D3" t="n">
-        <v>18792</v>
+        <v>18204</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2495</v>
+        <v>2179</v>
       </c>
       <c r="C4" t="n">
-        <v>11138</v>
+        <v>9470</v>
       </c>
       <c r="D4" t="n">
-        <v>9549</v>
+        <v>11088</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1337</v>
+        <v>1256</v>
       </c>
       <c r="C5" t="n">
-        <v>6590</v>
+        <v>5844</v>
       </c>
       <c r="D5" t="n">
-        <v>3022</v>
+        <v>3971</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>775</v>
+        <v>784</v>
       </c>
       <c r="C6" t="n">
-        <v>3656</v>
+        <v>3582</v>
       </c>
       <c r="D6" t="n">
-        <v>866</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="C7" t="n">
-        <v>2243</v>
+        <v>2234</v>
       </c>
       <c r="D7" t="n">
-        <v>500</v>
+        <v>518</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C8" t="n">
-        <v>1218</v>
+        <v>1133</v>
       </c>
       <c r="D8" t="n">
-        <v>331</v>
+        <v>336</v>
       </c>
     </row>
     <row r="9">
@@ -2125,10 +2125,10 @@
         <v>42</v>
       </c>
       <c r="C9" t="n">
-        <v>449</v>
+        <v>436</v>
       </c>
       <c r="D9" t="n">
-        <v>258</v>
+        <v>254</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="D10" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D17" t="n">
         <v>25</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3634</v>
+        <v>4505</v>
       </c>
       <c r="C2" t="n">
-        <v>6878</v>
+        <v>5851</v>
       </c>
       <c r="D2" t="n">
-        <v>18826</v>
+        <v>24891</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3687</v>
+        <v>3423</v>
       </c>
       <c r="C3" t="n">
-        <v>6788</v>
+        <v>4826</v>
       </c>
       <c r="D3" t="n">
-        <v>17721</v>
+        <v>16760</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2933</v>
+        <v>2616</v>
       </c>
       <c r="C4" t="n">
-        <v>10637</v>
+        <v>8518</v>
       </c>
       <c r="D4" t="n">
-        <v>10767</v>
+        <v>11912</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1589</v>
+        <v>1459</v>
       </c>
       <c r="C5" t="n">
-        <v>8504</v>
+        <v>7393</v>
       </c>
       <c r="D5" t="n">
-        <v>3932</v>
+        <v>4943</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>926</v>
+        <v>898</v>
       </c>
       <c r="C6" t="n">
-        <v>4889</v>
+        <v>4581</v>
       </c>
       <c r="D6" t="n">
-        <v>1165</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="C7" t="n">
-        <v>2859</v>
+        <v>2823</v>
       </c>
       <c r="D7" t="n">
-        <v>545</v>
+        <v>585</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C8" t="n">
-        <v>1631</v>
+        <v>1575</v>
       </c>
       <c r="D8" t="n">
-        <v>349</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>732</v>
+        <v>692</v>
       </c>
       <c r="D9" t="n">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="D10" t="n">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14">
@@ -2509,7 +2509,7 @@
         <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D17" t="n">
         <v>23</v>
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2217</v>
+        <v>2679</v>
       </c>
       <c r="C2" t="n">
-        <v>3333</v>
+        <v>2783</v>
       </c>
       <c r="D2" t="n">
-        <v>13144</v>
+        <v>17353</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3549</v>
+        <v>3546</v>
       </c>
       <c r="C3" t="n">
-        <v>6632</v>
+        <v>5023</v>
       </c>
       <c r="D3" t="n">
-        <v>17438</v>
+        <v>17230</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3198</v>
+        <v>2891</v>
       </c>
       <c r="C4" t="n">
-        <v>10254</v>
+        <v>7988</v>
       </c>
       <c r="D4" t="n">
-        <v>11595</v>
+        <v>12587</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1641</v>
+        <v>1537</v>
       </c>
       <c r="C5" t="n">
-        <v>10214</v>
+        <v>8799</v>
       </c>
       <c r="D5" t="n">
-        <v>4172</v>
+        <v>5197</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="C6" t="n">
-        <v>5735</v>
+        <v>5416</v>
       </c>
       <c r="D6" t="n">
-        <v>1149</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C7" t="n">
-        <v>2968</v>
+        <v>2934</v>
       </c>
       <c r="D7" t="n">
-        <v>551</v>
+        <v>583</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C8" t="n">
-        <v>1196</v>
+        <v>1141</v>
       </c>
       <c r="D8" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D11" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -2806,7 +2806,7 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D16" t="n">
         <v>22</v>
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2549</v>
+        <v>2523</v>
       </c>
       <c r="C2" t="n">
-        <v>2791</v>
+        <v>8847</v>
       </c>
       <c r="D2" t="n">
-        <v>11042</v>
+        <v>20291</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2566</v>
+        <v>2730</v>
       </c>
       <c r="C3" t="n">
-        <v>4654</v>
+        <v>3598</v>
       </c>
       <c r="D3" t="n">
-        <v>15744</v>
+        <v>16254</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2947</v>
+        <v>2749</v>
       </c>
       <c r="C4" t="n">
-        <v>8406</v>
+        <v>6455</v>
       </c>
       <c r="D4" t="n">
-        <v>12139</v>
+        <v>12917</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1987</v>
+        <v>1842</v>
       </c>
       <c r="C5" t="n">
-        <v>10116</v>
+        <v>8342</v>
       </c>
       <c r="D5" t="n">
-        <v>5114</v>
+        <v>6103</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>972</v>
+        <v>953</v>
       </c>
       <c r="C6" t="n">
-        <v>7546</v>
+        <v>6816</v>
       </c>
       <c r="D6" t="n">
-        <v>1551</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C7" t="n">
-        <v>4082</v>
+        <v>3963</v>
       </c>
       <c r="D7" t="n">
-        <v>615</v>
+        <v>674</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C8" t="n">
-        <v>1826</v>
+        <v>1795</v>
       </c>
       <c r="D8" t="n">
-        <v>392</v>
+        <v>397</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>582</v>
+        <v>568</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D10" t="n">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -3103,7 +3103,7 @@
         <v>80</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -3117,7 +3117,7 @@
         <v>58</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1785</v>
+        <v>1821</v>
       </c>
       <c r="C2" t="n">
-        <v>2796</v>
+        <v>4888</v>
       </c>
       <c r="D2" t="n">
-        <v>8280</v>
+        <v>14776</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2247</v>
+        <v>2337</v>
       </c>
       <c r="C3" t="n">
-        <v>3640</v>
+        <v>5152</v>
       </c>
       <c r="D3" t="n">
-        <v>14386</v>
+        <v>16010</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2595</v>
+        <v>2501</v>
       </c>
       <c r="C4" t="n">
-        <v>6951</v>
+        <v>5382</v>
       </c>
       <c r="D4" t="n">
-        <v>12336</v>
+        <v>13064</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2161</v>
+        <v>2013</v>
       </c>
       <c r="C5" t="n">
-        <v>9703</v>
+        <v>7756</v>
       </c>
       <c r="D5" t="n">
-        <v>5798</v>
+        <v>6754</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1125</v>
+        <v>1108</v>
       </c>
       <c r="C6" t="n">
-        <v>8607</v>
+        <v>7559</v>
       </c>
       <c r="D6" t="n">
-        <v>1836</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="C7" t="n">
-        <v>5141</v>
+        <v>4904</v>
       </c>
       <c r="D7" t="n">
-        <v>684</v>
+        <v>759</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
-        <v>2330</v>
+        <v>2304</v>
       </c>
       <c r="D8" t="n">
-        <v>407</v>
+        <v>412</v>
       </c>
     </row>
     <row r="9">
@@ -3369,7 +3369,7 @@
         <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D9" t="n">
         <v>288</v>
@@ -3383,7 +3383,7 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D10" t="n">
         <v>178</v>
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>35</v>
+      </c>
+      <c r="D14" t="n">
         <v>36</v>
-      </c>
-      <c r="D14" t="n">
-        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2700</v>
+        <v>2927</v>
       </c>
       <c r="C2" t="n">
-        <v>3407</v>
+        <v>7599</v>
       </c>
       <c r="D2" t="n">
-        <v>14143</v>
+        <v>15324</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1763</v>
+        <v>1818</v>
       </c>
       <c r="C3" t="n">
-        <v>2966</v>
+        <v>4500</v>
       </c>
       <c r="D3" t="n">
-        <v>12804</v>
+        <v>14990</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2154</v>
+        <v>2124</v>
       </c>
       <c r="C4" t="n">
-        <v>5471</v>
+        <v>5175</v>
       </c>
       <c r="D4" t="n">
-        <v>12236</v>
+        <v>12937</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2125</v>
+        <v>2005</v>
       </c>
       <c r="C5" t="n">
-        <v>8444</v>
+        <v>6660</v>
       </c>
       <c r="D5" t="n">
-        <v>6382</v>
+        <v>7396</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1337</v>
+        <v>1305</v>
       </c>
       <c r="C6" t="n">
-        <v>8937</v>
+        <v>7570</v>
       </c>
       <c r="D6" t="n">
-        <v>2306</v>
+        <v>2785</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C7" t="n">
-        <v>6361</v>
+        <v>5864</v>
       </c>
       <c r="D7" t="n">
-        <v>812</v>
+        <v>926</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>3288</v>
+        <v>3217</v>
       </c>
       <c r="D8" t="n">
-        <v>432</v>
+        <v>445</v>
       </c>
     </row>
     <row r="9">
@@ -3680,10 +3680,10 @@
         <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>1153</v>
+        <v>1169</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -3697,7 +3697,7 @@
         <v>342</v>
       </c>
       <c r="D10" t="n">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -3739,7 +3739,7 @@
         <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6169</v>
+        <v>5901</v>
       </c>
       <c r="C2" t="n">
-        <v>8979</v>
+        <v>9163</v>
       </c>
       <c r="D2" t="n">
-        <v>5621</v>
+        <v>17213</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1973</v>
+        <v>2115</v>
       </c>
       <c r="C2" t="n">
-        <v>2016</v>
+        <v>4437</v>
       </c>
       <c r="D2" t="n">
-        <v>10523</v>
+        <v>11402</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2412</v>
+        <v>2488</v>
       </c>
       <c r="C3" t="n">
-        <v>3380</v>
+        <v>5572</v>
       </c>
       <c r="D3" t="n">
-        <v>14023</v>
+        <v>16117</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3063</v>
+        <v>2919</v>
       </c>
       <c r="C4" t="n">
-        <v>8183</v>
+        <v>7530</v>
       </c>
       <c r="D4" t="n">
-        <v>12338</v>
+        <v>13325</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1255</v>
+        <v>1242</v>
       </c>
       <c r="C5" t="n">
-        <v>12531</v>
+        <v>10228</v>
       </c>
       <c r="D5" t="n">
-        <v>5747</v>
+        <v>6717</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C6" t="n">
-        <v>7810</v>
+        <v>7156</v>
       </c>
       <c r="D6" t="n">
-        <v>1807</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C7" t="n">
-        <v>3222</v>
+        <v>3152</v>
       </c>
       <c r="D7" t="n">
-        <v>518</v>
+        <v>554</v>
       </c>
     </row>
     <row r="8">
@@ -4288,10 +4288,10 @@
         <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>1129</v>
+        <v>1145</v>
       </c>
       <c r="D8" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="9">
@@ -4305,7 +4305,7 @@
         <v>335</v>
       </c>
       <c r="D9" t="n">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D10" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12">
@@ -4347,7 +4347,7 @@
         <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D13" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6208</v>
+        <v>6344</v>
       </c>
       <c r="C2" t="n">
-        <v>6894</v>
+        <v>4698</v>
       </c>
       <c r="D2" t="n">
-        <v>8810</v>
+        <v>20319</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2621</v>
+        <v>2507</v>
       </c>
       <c r="C3" t="n">
-        <v>4525</v>
+        <v>4618</v>
       </c>
       <c r="D3" t="n">
-        <v>1583</v>
+        <v>3531</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C8" t="n">
         <v>260</v>
@@ -4610,7 +4610,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
@@ -4697,7 +4697,7 @@
         <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
         <v>118</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4074</v>
+        <v>4316</v>
       </c>
       <c r="C2" t="n">
-        <v>7474</v>
+        <v>7403</v>
       </c>
       <c r="D2" t="n">
-        <v>13221</v>
+        <v>20480</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3627</v>
+        <v>3634</v>
       </c>
       <c r="C3" t="n">
-        <v>5058</v>
+        <v>4021</v>
       </c>
       <c r="D3" t="n">
-        <v>2680</v>
+        <v>6091</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1172</v>
+        <v>1123</v>
       </c>
       <c r="C4" t="n">
-        <v>2693</v>
+        <v>2750</v>
       </c>
       <c r="D4" t="n">
-        <v>1500</v>
+        <v>1893</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>859</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C8" t="n">
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
         <v>232</v>
@@ -4935,10 +4935,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
         <v>352</v>
@@ -4952,7 +4952,7 @@
         <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5025,7 +5025,7 @@
         <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4313</v>
+        <v>5381</v>
       </c>
       <c r="C2" t="n">
-        <v>4829</v>
+        <v>9037</v>
       </c>
       <c r="D2" t="n">
-        <v>21490</v>
+        <v>37711</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3173</v>
+        <v>3270</v>
       </c>
       <c r="C3" t="n">
-        <v>5518</v>
+        <v>5115</v>
       </c>
       <c r="D3" t="n">
-        <v>4173</v>
+        <v>7954</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2033</v>
+        <v>2024</v>
       </c>
       <c r="C4" t="n">
-        <v>3976</v>
+        <v>3374</v>
       </c>
       <c r="D4" t="n">
-        <v>1680</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>541</v>
+        <v>512</v>
       </c>
       <c r="C5" t="n">
-        <v>1568</v>
+        <v>1602</v>
       </c>
       <c r="D5" t="n">
-        <v>1195</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9" t="n">
         <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5277,10 +5277,10 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13">
@@ -5294,7 +5294,7 @@
         <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="14">
@@ -5305,7 +5305,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
         <v>148</v>
@@ -5316,10 +5316,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5336,7 +5336,7 @@
         <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4689</v>
+        <v>4822</v>
       </c>
       <c r="C2" t="n">
-        <v>7014</v>
+        <v>6523</v>
       </c>
       <c r="D2" t="n">
-        <v>29800</v>
+        <v>31193</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3054</v>
+        <v>3484</v>
       </c>
       <c r="C3" t="n">
-        <v>4494</v>
+        <v>6185</v>
       </c>
       <c r="D3" t="n">
-        <v>6511</v>
+        <v>11917</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2223</v>
+        <v>2230</v>
       </c>
       <c r="C4" t="n">
-        <v>4722</v>
+        <v>4190</v>
       </c>
       <c r="D4" t="n">
-        <v>2083</v>
+        <v>3529</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1059</v>
+        <v>1045</v>
       </c>
       <c r="C5" t="n">
-        <v>2768</v>
+        <v>2487</v>
       </c>
       <c r="D5" t="n">
-        <v>1231</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>298</v>
+        <v>282</v>
       </c>
       <c r="C6" t="n">
-        <v>942</v>
+        <v>949</v>
       </c>
       <c r="D6" t="n">
-        <v>946</v>
+        <v>959</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>666</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C9" t="n">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11">
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
         <v>286</v>
@@ -5588,10 +5588,10 @@
         <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D12" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D13" t="n">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14">
@@ -5616,10 +5616,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5633,7 +5633,7 @@
         <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7048</v>
+        <v>5279</v>
       </c>
       <c r="C2" t="n">
-        <v>13131</v>
+        <v>10517</v>
       </c>
       <c r="D2" t="n">
-        <v>29872</v>
+        <v>33805</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2797</v>
+        <v>2995</v>
       </c>
       <c r="C3" t="n">
-        <v>4736</v>
+        <v>5209</v>
       </c>
       <c r="D3" t="n">
-        <v>9023</v>
+        <v>13179</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1628</v>
+        <v>1749</v>
       </c>
       <c r="C4" t="n">
-        <v>3764</v>
+        <v>4280</v>
       </c>
       <c r="D4" t="n">
-        <v>2467</v>
+        <v>4322</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>864</v>
+        <v>849</v>
       </c>
       <c r="C5" t="n">
-        <v>2742</v>
+        <v>2460</v>
       </c>
       <c r="D5" t="n">
-        <v>1076</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="C6" t="n">
-        <v>1254</v>
+        <v>1151</v>
       </c>
       <c r="D6" t="n">
-        <v>756</v>
+        <v>795</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C7" t="n">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="D7" t="n">
-        <v>512</v>
+        <v>518</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>357</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
         <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14">
@@ -5927,7 +5927,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
         <v>96</v>
@@ -5944,7 +5944,7 @@
         <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
@@ -5955,10 +5955,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5685</v>
+        <v>5068</v>
       </c>
       <c r="C2" t="n">
-        <v>7143</v>
+        <v>6006</v>
       </c>
       <c r="D2" t="n">
-        <v>35018</v>
+        <v>26316</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4108</v>
+        <v>3420</v>
       </c>
       <c r="C3" t="n">
-        <v>8300</v>
+        <v>7116</v>
       </c>
       <c r="D3" t="n">
-        <v>11861</v>
+        <v>15674</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1942</v>
+        <v>2071</v>
       </c>
       <c r="C4" t="n">
-        <v>4273</v>
+        <v>4743</v>
       </c>
       <c r="D4" t="n">
-        <v>3690</v>
+        <v>5976</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1114</v>
+        <v>1145</v>
       </c>
       <c r="C5" t="n">
-        <v>3257</v>
+        <v>3433</v>
       </c>
       <c r="D5" t="n">
-        <v>1323</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="C6" t="n">
-        <v>2095</v>
+        <v>1878</v>
       </c>
       <c r="D6" t="n">
-        <v>806</v>
+        <v>904</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C7" t="n">
-        <v>888</v>
+        <v>821</v>
       </c>
       <c r="D7" t="n">
-        <v>547</v>
+        <v>559</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="D8" t="n">
-        <v>387</v>
+        <v>383</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
         <v>199</v>
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13">
@@ -6227,7 +6227,7 @@
         <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14">
@@ -6235,7 +6235,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
         <v>63</v>
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -6294,10 +6294,10 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6339,7 +6339,7 @@
         <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4508</v>
+        <v>4307</v>
       </c>
       <c r="C2" t="n">
-        <v>9124</v>
+        <v>4752</v>
       </c>
       <c r="D2" t="n">
-        <v>33266</v>
+        <v>27281</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4013</v>
+        <v>3461</v>
       </c>
       <c r="C3" t="n">
-        <v>6638</v>
+        <v>5655</v>
       </c>
       <c r="D3" t="n">
-        <v>14712</v>
+        <v>16248</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2591</v>
+        <v>2333</v>
       </c>
       <c r="C4" t="n">
-        <v>6465</v>
+        <v>5965</v>
       </c>
       <c r="D4" t="n">
-        <v>5146</v>
+        <v>7656</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1333</v>
+        <v>1411</v>
       </c>
       <c r="C5" t="n">
-        <v>3745</v>
+        <v>4065</v>
       </c>
       <c r="D5" t="n">
-        <v>1701</v>
+        <v>2603</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="C6" t="n">
-        <v>2684</v>
+        <v>2644</v>
       </c>
       <c r="D6" t="n">
-        <v>889</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="C7" t="n">
-        <v>1505</v>
+        <v>1369</v>
       </c>
       <c r="D7" t="n">
-        <v>587</v>
+        <v>614</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C8" t="n">
-        <v>610</v>
+        <v>570</v>
       </c>
       <c r="D8" t="n">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -6566,7 +6566,7 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6605,10 +6605,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>29</v>
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_85_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_85_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4612</v>
+        <v>871</v>
       </c>
       <c r="C2" t="n">
-        <v>12880</v>
+        <v>1991</v>
       </c>
       <c r="D2" t="n">
-        <v>25593</v>
+        <v>12761</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3167</v>
+        <v>1506</v>
       </c>
       <c r="C3" t="n">
-        <v>4566</v>
+        <v>6247</v>
       </c>
       <c r="D3" t="n">
-        <v>16718</v>
+        <v>13399</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2430</v>
+        <v>965</v>
       </c>
       <c r="C4" t="n">
-        <v>5683</v>
+        <v>9385</v>
       </c>
       <c r="D4" t="n">
-        <v>8907</v>
+        <v>5406</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1623</v>
+        <v>467</v>
       </c>
       <c r="C5" t="n">
-        <v>4871</v>
+        <v>5953</v>
       </c>
       <c r="D5" t="n">
-        <v>3323</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>952</v>
+        <v>212</v>
       </c>
       <c r="C6" t="n">
-        <v>3298</v>
+        <v>2168</v>
       </c>
       <c r="D6" t="n">
-        <v>1295</v>
+        <v>725</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>455</v>
+        <v>98</v>
       </c>
       <c r="C7" t="n">
-        <v>1954</v>
+        <v>777</v>
       </c>
       <c r="D7" t="n">
-        <v>671</v>
+        <v>485</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>175</v>
+        <v>73</v>
       </c>
       <c r="C8" t="n">
-        <v>937</v>
+        <v>354</v>
       </c>
       <c r="D8" t="n">
-        <v>432</v>
+        <v>373</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>395</v>
+        <v>287</v>
       </c>
       <c r="D9" t="n">
-        <v>306</v>
+        <v>314</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>142</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5418</v>
+        <v>1464</v>
       </c>
       <c r="C2" t="n">
-        <v>12435</v>
+        <v>13337</v>
       </c>
       <c r="D2" t="n">
-        <v>24610</v>
+        <v>17233</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3131</v>
+        <v>1020</v>
       </c>
       <c r="C3" t="n">
-        <v>7284</v>
+        <v>3486</v>
       </c>
       <c r="D3" t="n">
-        <v>16962</v>
+        <v>12358</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2342</v>
+        <v>1058</v>
       </c>
       <c r="C4" t="n">
-        <v>5039</v>
+        <v>7562</v>
       </c>
       <c r="D4" t="n">
-        <v>9750</v>
+        <v>6699</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1737</v>
+        <v>612</v>
       </c>
       <c r="C5" t="n">
-        <v>5089</v>
+        <v>7665</v>
       </c>
       <c r="D5" t="n">
-        <v>4079</v>
+        <v>2284</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1124</v>
+        <v>297</v>
       </c>
       <c r="C6" t="n">
-        <v>3960</v>
+        <v>3998</v>
       </c>
       <c r="D6" t="n">
-        <v>1557</v>
+        <v>873</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>598</v>
+        <v>132</v>
       </c>
       <c r="C7" t="n">
-        <v>2513</v>
+        <v>1452</v>
       </c>
       <c r="D7" t="n">
-        <v>755</v>
+        <v>517</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>253</v>
+        <v>77</v>
       </c>
       <c r="C8" t="n">
-        <v>1365</v>
+        <v>551</v>
       </c>
       <c r="D8" t="n">
-        <v>456</v>
+        <v>389</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="C9" t="n">
-        <v>608</v>
+        <v>317</v>
       </c>
       <c r="D9" t="n">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="C10" t="n">
-        <v>287</v>
+        <v>244</v>
       </c>
       <c r="D10" t="n">
-        <v>247</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>96</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6780</v>
+        <v>773</v>
       </c>
       <c r="C2" t="n">
-        <v>7810</v>
+        <v>5571</v>
       </c>
       <c r="D2" t="n">
-        <v>27491</v>
+        <v>11771</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3284</v>
+        <v>1110</v>
       </c>
       <c r="C3" t="n">
-        <v>8292</v>
+        <v>7129</v>
       </c>
       <c r="D3" t="n">
-        <v>16794</v>
+        <v>12626</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2264</v>
+        <v>1148</v>
       </c>
       <c r="C4" t="n">
-        <v>5834</v>
+        <v>6638</v>
       </c>
       <c r="D4" t="n">
-        <v>10398</v>
+        <v>7414</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1777</v>
+        <v>617</v>
       </c>
       <c r="C5" t="n">
-        <v>4913</v>
+        <v>8548</v>
       </c>
       <c r="D5" t="n">
-        <v>4771</v>
+        <v>2591</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1241</v>
+        <v>253</v>
       </c>
       <c r="C6" t="n">
-        <v>4380</v>
+        <v>5086</v>
       </c>
       <c r="D6" t="n">
-        <v>1860</v>
+        <v>895</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>718</v>
+        <v>71</v>
       </c>
       <c r="C7" t="n">
-        <v>3054</v>
+        <v>1370</v>
       </c>
       <c r="D7" t="n">
-        <v>857</v>
+        <v>550</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>338</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>1789</v>
+        <v>505</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>433</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>134</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>889</v>
+        <v>239</v>
       </c>
       <c r="D9" t="n">
-        <v>334</v>
+        <v>369</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>397</v>
+        <v>188</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>216</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>152</v>
+        <v>86</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>114</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>129</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>94</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6186</v>
+        <v>504</v>
       </c>
       <c r="C2" t="n">
-        <v>5373</v>
+        <v>6448</v>
       </c>
       <c r="D2" t="n">
-        <v>22798</v>
+        <v>12281</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3971</v>
+        <v>817</v>
       </c>
       <c r="C3" t="n">
-        <v>11299</v>
+        <v>5599</v>
       </c>
       <c r="D3" t="n">
-        <v>18510</v>
+        <v>11728</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1641</v>
+        <v>1003</v>
       </c>
       <c r="C4" t="n">
-        <v>7852</v>
+        <v>6818</v>
       </c>
       <c r="D4" t="n">
-        <v>10085</v>
+        <v>8089</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1146</v>
+        <v>752</v>
       </c>
       <c r="C5" t="n">
-        <v>4292</v>
+        <v>7517</v>
       </c>
       <c r="D5" t="n">
-        <v>3105</v>
+        <v>3299</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>663</v>
+        <v>363</v>
       </c>
       <c r="C6" t="n">
-        <v>2992</v>
+        <v>6680</v>
       </c>
       <c r="D6" t="n">
-        <v>839</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>312</v>
+        <v>119</v>
       </c>
       <c r="C7" t="n">
-        <v>1753</v>
+        <v>3035</v>
       </c>
       <c r="D7" t="n">
-        <v>474</v>
+        <v>597</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>123</v>
+        <v>55</v>
       </c>
       <c r="C8" t="n">
-        <v>871</v>
+        <v>867</v>
       </c>
       <c r="D8" t="n">
-        <v>327</v>
+        <v>442</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="C9" t="n">
-        <v>389</v>
+        <v>339</v>
       </c>
       <c r="D9" t="n">
-        <v>245</v>
+        <v>379</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>201</v>
+        <v>225</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>175</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="D12" t="n">
-        <v>126</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>62</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>92</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3911</v>
+        <v>339</v>
       </c>
       <c r="C2" t="n">
-        <v>2538</v>
+        <v>4039</v>
       </c>
       <c r="D2" t="n">
-        <v>16588</v>
+        <v>9779</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4196</v>
+        <v>616</v>
       </c>
       <c r="C3" t="n">
-        <v>7898</v>
+        <v>5427</v>
       </c>
       <c r="D3" t="n">
-        <v>18204</v>
+        <v>11240</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2179</v>
+        <v>869</v>
       </c>
       <c r="C4" t="n">
-        <v>9470</v>
+        <v>6322</v>
       </c>
       <c r="D4" t="n">
-        <v>11088</v>
+        <v>8444</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1256</v>
+        <v>805</v>
       </c>
       <c r="C5" t="n">
-        <v>5844</v>
+        <v>7367</v>
       </c>
       <c r="D5" t="n">
-        <v>3971</v>
+        <v>3859</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>784</v>
+        <v>438</v>
       </c>
       <c r="C6" t="n">
-        <v>3582</v>
+        <v>7245</v>
       </c>
       <c r="D6" t="n">
-        <v>1049</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>292</v>
+        <v>130</v>
       </c>
       <c r="C7" t="n">
-        <v>2234</v>
+        <v>4277</v>
       </c>
       <c r="D7" t="n">
-        <v>518</v>
+        <v>655</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>104</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>1133</v>
+        <v>1379</v>
       </c>
       <c r="D8" t="n">
-        <v>336</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D9" t="n">
-        <v>254</v>
+        <v>379</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>231</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>183</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>98</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4505</v>
+        <v>419</v>
       </c>
       <c r="C2" t="n">
-        <v>5851</v>
+        <v>6503</v>
       </c>
       <c r="D2" t="n">
-        <v>24891</v>
+        <v>12193</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3423</v>
+        <v>426</v>
       </c>
       <c r="C3" t="n">
-        <v>4826</v>
+        <v>4240</v>
       </c>
       <c r="D3" t="n">
-        <v>16760</v>
+        <v>10393</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2616</v>
+        <v>676</v>
       </c>
       <c r="C4" t="n">
-        <v>8518</v>
+        <v>5769</v>
       </c>
       <c r="D4" t="n">
-        <v>11912</v>
+        <v>8535</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1459</v>
+        <v>764</v>
       </c>
       <c r="C5" t="n">
-        <v>7393</v>
+        <v>6812</v>
       </c>
       <c r="D5" t="n">
-        <v>4943</v>
+        <v>4445</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>898</v>
+        <v>532</v>
       </c>
       <c r="C6" t="n">
-        <v>4581</v>
+        <v>7229</v>
       </c>
       <c r="D6" t="n">
-        <v>1455</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>426</v>
+        <v>211</v>
       </c>
       <c r="C7" t="n">
-        <v>2823</v>
+        <v>5538</v>
       </c>
       <c r="D7" t="n">
-        <v>585</v>
+        <v>745</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>148</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>1575</v>
+        <v>2486</v>
       </c>
       <c r="D8" t="n">
-        <v>355</v>
+        <v>489</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="C9" t="n">
-        <v>692</v>
+        <v>781</v>
       </c>
       <c r="D9" t="n">
-        <v>263</v>
+        <v>389</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>243</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>102</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>92</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>98</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2679</v>
+        <v>288</v>
       </c>
       <c r="C2" t="n">
-        <v>2783</v>
+        <v>3485</v>
       </c>
       <c r="D2" t="n">
-        <v>17353</v>
+        <v>8877</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3546</v>
+        <v>605</v>
       </c>
       <c r="C3" t="n">
-        <v>5023</v>
+        <v>5176</v>
       </c>
       <c r="D3" t="n">
-        <v>17230</v>
+        <v>11346</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2891</v>
+        <v>1043</v>
       </c>
       <c r="C4" t="n">
-        <v>7988</v>
+        <v>7979</v>
       </c>
       <c r="D4" t="n">
-        <v>12587</v>
+        <v>8683</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1537</v>
+        <v>533</v>
       </c>
       <c r="C5" t="n">
-        <v>8799</v>
+        <v>10092</v>
       </c>
       <c r="D5" t="n">
-        <v>5197</v>
+        <v>4104</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>750</v>
+        <v>194</v>
       </c>
       <c r="C6" t="n">
-        <v>5416</v>
+        <v>7127</v>
       </c>
       <c r="D6" t="n">
-        <v>1412</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>136</v>
+        <v>63</v>
       </c>
       <c r="C7" t="n">
-        <v>2934</v>
+        <v>2436</v>
       </c>
       <c r="D7" t="n">
-        <v>583</v>
+        <v>581</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="C8" t="n">
-        <v>1141</v>
+        <v>765</v>
       </c>
       <c r="D8" t="n">
-        <v>375</v>
+        <v>381</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D9" t="n">
-        <v>285</v>
+        <v>238</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="D11" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>96</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2523</v>
+        <v>210</v>
       </c>
       <c r="C2" t="n">
-        <v>8847</v>
+        <v>2154</v>
       </c>
       <c r="D2" t="n">
-        <v>20291</v>
+        <v>6696</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2730</v>
+        <v>401</v>
       </c>
       <c r="C3" t="n">
-        <v>3598</v>
+        <v>3848</v>
       </c>
       <c r="D3" t="n">
-        <v>16254</v>
+        <v>10177</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2749</v>
+        <v>705</v>
       </c>
       <c r="C4" t="n">
-        <v>6455</v>
+        <v>6231</v>
       </c>
       <c r="D4" t="n">
-        <v>12917</v>
+        <v>8588</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1842</v>
+        <v>522</v>
       </c>
       <c r="C5" t="n">
-        <v>8342</v>
+        <v>8083</v>
       </c>
       <c r="D5" t="n">
-        <v>6103</v>
+        <v>4211</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>953</v>
+        <v>189</v>
       </c>
       <c r="C6" t="n">
-        <v>6816</v>
+        <v>6864</v>
       </c>
       <c r="D6" t="n">
-        <v>1916</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>279</v>
+        <v>50</v>
       </c>
       <c r="C7" t="n">
-        <v>3963</v>
+        <v>3161</v>
       </c>
       <c r="D7" t="n">
-        <v>674</v>
+        <v>557</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>1795</v>
+        <v>902</v>
       </c>
       <c r="D8" t="n">
-        <v>397</v>
+        <v>329</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>568</v>
+        <v>276</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>217</v>
+        <v>124</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>128</v>
+        <v>75</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>80</v>
+        <v>53</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1821</v>
+        <v>64</v>
       </c>
       <c r="C2" t="n">
-        <v>4888</v>
+        <v>10285</v>
       </c>
       <c r="D2" t="n">
-        <v>14776</v>
+        <v>8583</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2337</v>
+        <v>260</v>
       </c>
       <c r="C3" t="n">
-        <v>5152</v>
+        <v>2570</v>
       </c>
       <c r="D3" t="n">
-        <v>16010</v>
+        <v>8931</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2501</v>
+        <v>496</v>
       </c>
       <c r="C4" t="n">
-        <v>5382</v>
+        <v>4797</v>
       </c>
       <c r="D4" t="n">
-        <v>13064</v>
+        <v>8616</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2013</v>
+        <v>548</v>
       </c>
       <c r="C5" t="n">
-        <v>7756</v>
+        <v>7014</v>
       </c>
       <c r="D5" t="n">
-        <v>6754</v>
+        <v>4839</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1108</v>
+        <v>306</v>
       </c>
       <c r="C6" t="n">
-        <v>7559</v>
+        <v>7398</v>
       </c>
       <c r="D6" t="n">
-        <v>2252</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>251</v>
+        <v>96</v>
       </c>
       <c r="C7" t="n">
-        <v>4904</v>
+        <v>5005</v>
       </c>
       <c r="D7" t="n">
-        <v>759</v>
+        <v>707</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="C8" t="n">
-        <v>2304</v>
+        <v>1950</v>
       </c>
       <c r="D8" t="n">
-        <v>412</v>
+        <v>359</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>642</v>
+        <v>548</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>204</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>220</v>
+        <v>186</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>127</v>
+        <v>94</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2927</v>
+        <v>148</v>
       </c>
       <c r="C2" t="n">
-        <v>7599</v>
+        <v>8102</v>
       </c>
       <c r="D2" t="n">
-        <v>15324</v>
+        <v>9558</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1818</v>
+        <v>148</v>
       </c>
       <c r="C3" t="n">
-        <v>4500</v>
+        <v>5462</v>
       </c>
       <c r="D3" t="n">
-        <v>14990</v>
+        <v>8266</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2124</v>
+        <v>344</v>
       </c>
       <c r="C4" t="n">
-        <v>5175</v>
+        <v>3585</v>
       </c>
       <c r="D4" t="n">
-        <v>12937</v>
+        <v>8408</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2005</v>
+        <v>477</v>
       </c>
       <c r="C5" t="n">
-        <v>6660</v>
+        <v>5803</v>
       </c>
       <c r="D5" t="n">
-        <v>7396</v>
+        <v>5308</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1305</v>
+        <v>377</v>
       </c>
       <c r="C6" t="n">
-        <v>7570</v>
+        <v>7147</v>
       </c>
       <c r="D6" t="n">
-        <v>2785</v>
+        <v>2363</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>452</v>
+        <v>164</v>
       </c>
       <c r="C7" t="n">
-        <v>5864</v>
+        <v>6032</v>
       </c>
       <c r="D7" t="n">
-        <v>926</v>
+        <v>897</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>94</v>
+        <v>47</v>
       </c>
       <c r="C8" t="n">
-        <v>3217</v>
+        <v>3296</v>
       </c>
       <c r="D8" t="n">
-        <v>445</v>
+        <v>406</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>1169</v>
+        <v>1138</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>221</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>342</v>
+        <v>331</v>
       </c>
       <c r="D10" t="n">
-        <v>185</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5901</v>
+        <v>2795</v>
       </c>
       <c r="C2" t="n">
-        <v>9163</v>
+        <v>11113</v>
       </c>
       <c r="D2" t="n">
-        <v>17213</v>
+        <v>7016</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2115</v>
+        <v>524</v>
       </c>
       <c r="C2" t="n">
-        <v>4437</v>
+        <v>21269</v>
       </c>
       <c r="D2" t="n">
-        <v>11402</v>
+        <v>14218</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2488</v>
+        <v>123</v>
       </c>
       <c r="C3" t="n">
-        <v>5572</v>
+        <v>5825</v>
       </c>
       <c r="D3" t="n">
-        <v>16117</v>
+        <v>7889</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2919</v>
+        <v>230</v>
       </c>
       <c r="C4" t="n">
-        <v>7530</v>
+        <v>4357</v>
       </c>
       <c r="D4" t="n">
-        <v>13325</v>
+        <v>8130</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1242</v>
+        <v>393</v>
       </c>
       <c r="C5" t="n">
-        <v>10228</v>
+        <v>4668</v>
       </c>
       <c r="D5" t="n">
-        <v>6717</v>
+        <v>5542</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>417</v>
+        <v>385</v>
       </c>
       <c r="C6" t="n">
-        <v>7156</v>
+        <v>6513</v>
       </c>
       <c r="D6" t="n">
-        <v>2126</v>
+        <v>2755</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>86</v>
+        <v>223</v>
       </c>
       <c r="C7" t="n">
-        <v>3152</v>
+        <v>6429</v>
       </c>
       <c r="D7" t="n">
-        <v>554</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="C8" t="n">
-        <v>1145</v>
+        <v>4394</v>
       </c>
       <c r="D8" t="n">
-        <v>291</v>
+        <v>469</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>335</v>
+        <v>1962</v>
       </c>
       <c r="D9" t="n">
-        <v>181</v>
+        <v>240</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>147</v>
+        <v>620</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>87</v>
+        <v>200</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6344</v>
+        <v>3317</v>
       </c>
       <c r="C2" t="n">
-        <v>4698</v>
+        <v>10431</v>
       </c>
       <c r="D2" t="n">
-        <v>20319</v>
+        <v>9775</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2507</v>
+        <v>926</v>
       </c>
       <c r="C3" t="n">
-        <v>4618</v>
+        <v>4388</v>
       </c>
       <c r="D3" t="n">
-        <v>3531</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>334</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>454</v>
+        <v>360</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4316</v>
+        <v>1940</v>
       </c>
       <c r="C2" t="n">
-        <v>7403</v>
+        <v>6145</v>
       </c>
       <c r="D2" t="n">
-        <v>20480</v>
+        <v>15635</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3634</v>
+        <v>1795</v>
       </c>
       <c r="C3" t="n">
-        <v>4021</v>
+        <v>6898</v>
       </c>
       <c r="D3" t="n">
-        <v>6091</v>
+        <v>2903</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1123</v>
+        <v>455</v>
       </c>
       <c r="C4" t="n">
-        <v>2750</v>
+        <v>2785</v>
       </c>
       <c r="D4" t="n">
-        <v>1893</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>98</v>
       </c>
       <c r="C5" t="n">
-        <v>225</v>
+        <v>206</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>756</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>406</v>
+        <v>324</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>116</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>245</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>190</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>186</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5381</v>
+        <v>1184</v>
       </c>
       <c r="C2" t="n">
-        <v>9037</v>
+        <v>10793</v>
       </c>
       <c r="D2" t="n">
-        <v>37711</v>
+        <v>22589</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3270</v>
+        <v>1541</v>
       </c>
       <c r="C3" t="n">
-        <v>5115</v>
+        <v>5547</v>
       </c>
       <c r="D3" t="n">
-        <v>7954</v>
+        <v>4828</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2024</v>
+        <v>989</v>
       </c>
       <c r="C4" t="n">
-        <v>3374</v>
+        <v>5214</v>
       </c>
       <c r="D4" t="n">
-        <v>2641</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>512</v>
+        <v>240</v>
       </c>
       <c r="C5" t="n">
-        <v>1602</v>
+        <v>1711</v>
       </c>
       <c r="D5" t="n">
-        <v>1276</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>111</v>
       </c>
       <c r="C6" t="n">
-        <v>305</v>
+        <v>259</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>799</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>117</v>
       </c>
       <c r="C7" t="n">
-        <v>401</v>
+        <v>335</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>549</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>126</v>
+        <v>91</v>
       </c>
       <c r="C8" t="n">
-        <v>357</v>
+        <v>286</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>217</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>174</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>193</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4822</v>
+        <v>1459</v>
       </c>
       <c r="C2" t="n">
-        <v>6523</v>
+        <v>9142</v>
       </c>
       <c r="D2" t="n">
-        <v>31193</v>
+        <v>31596</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3484</v>
+        <v>1130</v>
       </c>
       <c r="C3" t="n">
-        <v>6185</v>
+        <v>7310</v>
       </c>
       <c r="D3" t="n">
-        <v>11917</v>
+        <v>7322</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2230</v>
+        <v>1094</v>
       </c>
       <c r="C4" t="n">
-        <v>4190</v>
+        <v>5297</v>
       </c>
       <c r="D4" t="n">
-        <v>3529</v>
+        <v>2235</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1045</v>
+        <v>524</v>
       </c>
       <c r="C5" t="n">
-        <v>2487</v>
+        <v>3625</v>
       </c>
       <c r="D5" t="n">
-        <v>1460</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>282</v>
+        <v>158</v>
       </c>
       <c r="C6" t="n">
-        <v>949</v>
+        <v>1036</v>
       </c>
       <c r="D6" t="n">
-        <v>959</v>
+        <v>837</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>349</v>
+        <v>294</v>
       </c>
       <c r="D7" t="n">
-        <v>666</v>
+        <v>582</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>96</v>
       </c>
       <c r="C8" t="n">
-        <v>377</v>
+        <v>310</v>
       </c>
       <c r="D8" t="n">
-        <v>471</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="C9" t="n">
-        <v>308</v>
+        <v>250</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>194</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>159</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>101</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5279</v>
+        <v>2648</v>
       </c>
       <c r="C2" t="n">
-        <v>10517</v>
+        <v>6756</v>
       </c>
       <c r="D2" t="n">
-        <v>33805</v>
+        <v>27465</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2995</v>
+        <v>1058</v>
       </c>
       <c r="C3" t="n">
-        <v>5209</v>
+        <v>7183</v>
       </c>
       <c r="D3" t="n">
-        <v>13179</v>
+        <v>10496</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1749</v>
+        <v>965</v>
       </c>
       <c r="C4" t="n">
-        <v>4280</v>
+        <v>6269</v>
       </c>
       <c r="D4" t="n">
-        <v>4322</v>
+        <v>3094</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>849</v>
+        <v>695</v>
       </c>
       <c r="C5" t="n">
-        <v>2460</v>
+        <v>4416</v>
       </c>
       <c r="D5" t="n">
-        <v>1424</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>312</v>
+        <v>292</v>
       </c>
       <c r="C6" t="n">
-        <v>1151</v>
+        <v>2307</v>
       </c>
       <c r="D6" t="n">
-        <v>795</v>
+        <v>877</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>92</v>
+        <v>120</v>
       </c>
       <c r="C7" t="n">
-        <v>404</v>
+        <v>664</v>
       </c>
       <c r="D7" t="n">
-        <v>518</v>
+        <v>618</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>302</v>
       </c>
       <c r="D8" t="n">
-        <v>357</v>
+        <v>442</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>196</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>348</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>218</v>
       </c>
       <c r="D10" t="n">
-        <v>233</v>
+        <v>307</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>113</v>
+        <v>173</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>142</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>204</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>118</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,10 +6022,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5068</v>
+        <v>1809</v>
       </c>
       <c r="C2" t="n">
-        <v>6006</v>
+        <v>7260</v>
       </c>
       <c r="D2" t="n">
-        <v>26316</v>
+        <v>23760</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3420</v>
+        <v>1436</v>
       </c>
       <c r="C3" t="n">
-        <v>7116</v>
+        <v>6120</v>
       </c>
       <c r="D3" t="n">
-        <v>15674</v>
+        <v>12217</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2071</v>
+        <v>873</v>
       </c>
       <c r="C4" t="n">
-        <v>4743</v>
+        <v>6534</v>
       </c>
       <c r="D4" t="n">
-        <v>5976</v>
+        <v>4279</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1145</v>
+        <v>724</v>
       </c>
       <c r="C5" t="n">
-        <v>3433</v>
+        <v>5231</v>
       </c>
       <c r="D5" t="n">
-        <v>1923</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>537</v>
+        <v>427</v>
       </c>
       <c r="C6" t="n">
-        <v>1878</v>
+        <v>3275</v>
       </c>
       <c r="D6" t="n">
-        <v>904</v>
+        <v>931</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C7" t="n">
-        <v>821</v>
+        <v>1413</v>
       </c>
       <c r="D7" t="n">
-        <v>559</v>
+        <v>652</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="C8" t="n">
-        <v>320</v>
+        <v>465</v>
       </c>
       <c r="D8" t="n">
-        <v>383</v>
+        <v>459</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>209</v>
+        <v>287</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>358</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="C10" t="n">
-        <v>172</v>
+        <v>242</v>
       </c>
       <c r="D10" t="n">
-        <v>234</v>
+        <v>306</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>188</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>265</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>100</v>
+        <v>153</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>209</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>126</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6333,10 +6333,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4307</v>
+        <v>1679</v>
       </c>
       <c r="C2" t="n">
-        <v>4752</v>
+        <v>4530</v>
       </c>
       <c r="D2" t="n">
-        <v>27281</v>
+        <v>18672</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3461</v>
+        <v>1734</v>
       </c>
       <c r="C3" t="n">
-        <v>5655</v>
+        <v>9348</v>
       </c>
       <c r="D3" t="n">
-        <v>16248</v>
+        <v>13255</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2333</v>
+        <v>668</v>
       </c>
       <c r="C4" t="n">
-        <v>5965</v>
+        <v>9098</v>
       </c>
       <c r="D4" t="n">
-        <v>7656</v>
+        <v>3928</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1411</v>
+        <v>394</v>
       </c>
       <c r="C5" t="n">
-        <v>4065</v>
+        <v>3209</v>
       </c>
       <c r="D5" t="n">
-        <v>2603</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>753</v>
+        <v>159</v>
       </c>
       <c r="C6" t="n">
-        <v>2644</v>
+        <v>1384</v>
       </c>
       <c r="D6" t="n">
-        <v>1058</v>
+        <v>638</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>315</v>
+        <v>89</v>
       </c>
       <c r="C7" t="n">
-        <v>1369</v>
+        <v>455</v>
       </c>
       <c r="D7" t="n">
-        <v>614</v>
+        <v>449</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>107</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>570</v>
+        <v>281</v>
       </c>
       <c r="D8" t="n">
-        <v>404</v>
+        <v>350</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>262</v>
+        <v>237</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>145</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
